--- a/data/trans_camb/IP16A08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 7,4</t>
+          <t>-6,5; 6,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 8,88</t>
+          <t>-5,27; 8,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 0,0</t>
+          <t>-13,18; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,91; -2,15</t>
+          <t>-23,62; -1,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 9,78</t>
+          <t>-17,6; 10,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,79; -4,6</t>
+          <t>-25,02; -4,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 0,32</t>
+          <t>-12,18; 0,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 6,32</t>
+          <t>-8,56; 6,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -2,5</t>
+          <t>-15,38; -3,4</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,49</t>
+          <t>-87,32; 379,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,97</t>
+          <t>-100,0; 48,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,13; 226,99</t>
+          <t>-75,0; 258,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 4,11</t>
+          <t>-18,12; 5,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 1,15</t>
+          <t>-20,89; 1,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 2,62</t>
+          <t>-20,16; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,25</t>
+          <t>-13,19; 5,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 13,31</t>
+          <t>-8,23; 13,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 13,84</t>
+          <t>-8,66; 14,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 2,39</t>
+          <t>-12,68; 2,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 4,14</t>
+          <t>-12,52; 3,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 6,44</t>
+          <t>-10,86; 5,28</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,18; 75,73</t>
+          <t>-82,66; 81,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,59; 64,22</t>
+          <t>-92,66; 44,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,57; 53,59</t>
+          <t>-87,9; 57,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 120,26</t>
+          <t>-75,67; 116,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,99; 249,49</t>
+          <t>-60,58; 272,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 224,69</t>
+          <t>-60,6; 277,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 30,18</t>
+          <t>-69,14; 31,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 53,46</t>
+          <t>-71,64; 38,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 74,84</t>
+          <t>-63,67; 59,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 9,81</t>
+          <t>-25,18; 11,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 17,84</t>
+          <t>-18,61; 18,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 6,45</t>
+          <t>-29,79; 7,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 26,72</t>
+          <t>-11,97; 26,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 13,9</t>
+          <t>-21,74; 14,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 2,77</t>
+          <t>-26,88; 3,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 13,36</t>
+          <t>-14,11; 13,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 10,0</t>
+          <t>-14,71; 11,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 2,07</t>
+          <t>-22,44; 0,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,16; 74,17</t>
+          <t>-70,16; 105,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,06; 139,19</t>
+          <t>-54,94; 147,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,81; 64,02</t>
+          <t>-75,85; 89,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 228,86</t>
+          <t>-45,47; 239,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 151,51</t>
+          <t>-68,62; 134,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,07; 44,79</t>
+          <t>-82,77; 37,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 81,84</t>
+          <t>-45,54; 78,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 68,38</t>
+          <t>-46,33; 80,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 17,82</t>
+          <t>-73,87; 2,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 18,06</t>
+          <t>-14,46; 21,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 23,67</t>
+          <t>-16,04; 22,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,71; -1,67</t>
+          <t>-29,63; 0,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 21,08</t>
+          <t>-15,35; 19,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 16,25</t>
+          <t>-18,86; 15,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 1,64</t>
+          <t>-24,41; 1,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 15,65</t>
+          <t>-9,55; 15,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 13,27</t>
+          <t>-12,01; 14,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,67; -3,92</t>
+          <t>-22,18; -3,47</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,89; 144,08</t>
+          <t>-51,62; 184,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,72; 211,31</t>
+          <t>-62,3; 177,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,44; -11,75</t>
+          <t>-91,55; 0,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 144,0</t>
+          <t>-55,98; 129,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 109,87</t>
+          <t>-69,12; 94,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,28; 16,23</t>
+          <t>-79,9; 19,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 96,75</t>
+          <t>-36,61; 91,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 84,36</t>
+          <t>-46,92; 79,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,48; -24,92</t>
+          <t>-80,36; -22,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 3,17</t>
+          <t>-9,8; 4,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 6,01</t>
+          <t>-9,26; 5,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -0,96</t>
+          <t>-13,71; -0,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 3,19</t>
+          <t>-10,07; 3,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 5,9</t>
+          <t>-9,1; 5,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 0,49</t>
+          <t>-12,45; 0,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,6</t>
+          <t>-8,1; 1,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,6</t>
+          <t>-6,57; 3,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -1,79</t>
+          <t>-11,23; -1,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 27,69</t>
+          <t>-51,46; 40,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 50,37</t>
+          <t>-47,77; 52,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,9; -7,28</t>
+          <t>-74,15; 0,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 29,04</t>
+          <t>-52,22; 26,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 46,29</t>
+          <t>-45,97; 46,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 3,61</t>
+          <t>-63,05; 4,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 14,17</t>
+          <t>-44,43; 12,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 35,96</t>
+          <t>-35,86; 30,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,31; -12,29</t>
+          <t>-61,91; -12,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 6,67</t>
+          <t>-5,88; 6,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 8,93</t>
+          <t>-5,33; 9,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 0,0</t>
+          <t>-12,62; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,62; -1,45</t>
+          <t>-23,61; -1,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 10,9</t>
+          <t>-17,17; 10,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -4,45</t>
+          <t>-24,44; -4,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 0,37</t>
+          <t>-12,62; 0,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 6,75</t>
+          <t>-10,18; 6,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -3,4</t>
+          <t>-14,82; -2,66</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,32; 379,1</t>
+          <t>-100,0; 275,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,72</t>
+          <t>-100,0; 50,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,0; 258,16</t>
+          <t>-84,55; 203,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 5,68</t>
+          <t>-17,73; 4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 1,43</t>
+          <t>-21,52; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 2,9</t>
+          <t>-19,27; 3,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 5,65</t>
+          <t>-12,31; 5,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 13,13</t>
+          <t>-8,65; 13,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 14,62</t>
+          <t>-8,14; 14,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 2,25</t>
+          <t>-11,6; 2,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 3,21</t>
+          <t>-11,38; 4,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 5,28</t>
+          <t>-10,58; 5,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 81,04</t>
+          <t>-81,0; 67,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,66; 44,3</t>
+          <t>-92,73; 53,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,9; 57,62</t>
+          <t>-87,42; 56,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-75,67; 116,16</t>
+          <t>-71,96; 104,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 272,32</t>
+          <t>-59,04; 236,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 277,65</t>
+          <t>-56,89; 267,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 31,56</t>
+          <t>-66,88; 28,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,64; 38,79</t>
+          <t>-68,89; 67,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,67; 59,07</t>
+          <t>-61,37; 56,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 11,57</t>
+          <t>-26,79; 12,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 18,53</t>
+          <t>-20,95; 18,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 7,13</t>
+          <t>-27,54; 7,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 26,42</t>
+          <t>-14,16; 25,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 14,93</t>
+          <t>-19,11; 15,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 3,33</t>
+          <t>-28,11; 2,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 13,4</t>
+          <t>-13,84; 13,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 11,76</t>
+          <t>-15,1; 10,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 0,31</t>
+          <t>-22,69; 0,62</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 105,61</t>
+          <t>-75,12; 99,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 147,61</t>
+          <t>-58,37; 143,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,85; 89,77</t>
+          <t>-77,29; 67,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 239,09</t>
+          <t>-46,62; 208,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 134,57</t>
+          <t>-63,16; 138,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,77; 37,63</t>
+          <t>-84,62; 45,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 78,25</t>
+          <t>-46,6; 75,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 80,53</t>
+          <t>-48,33; 69,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,87; 2,35</t>
+          <t>-71,76; 8,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 21,07</t>
+          <t>-14,03; 20,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 22,77</t>
+          <t>-16,3; 22,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 0,2</t>
+          <t>-29,33; -0,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 19,49</t>
+          <t>-16,08; 20,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 15,29</t>
+          <t>-19,82; 14,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 1,94</t>
+          <t>-26,34; 0,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 15,02</t>
+          <t>-10,86; 14,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 14,28</t>
+          <t>-11,55; 15,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -3,47</t>
+          <t>-22,83; -3,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 184,84</t>
+          <t>-54,49; 191,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 177,14</t>
+          <t>-59,66; 186,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,55; 0,05</t>
+          <t>-92,88; 1,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 129,45</t>
+          <t>-56,95; 139,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,12; 94,04</t>
+          <t>-67,37; 93,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,9; 19,95</t>
+          <t>-81,17; 10,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 91,0</t>
+          <t>-42,79; 92,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 79,41</t>
+          <t>-46,45; 91,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,36; -22,62</t>
+          <t>-81,68; -22,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 4,34</t>
+          <t>-10,43; 2,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 5,87</t>
+          <t>-8,83; 6,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,03</t>
+          <t>-14,55; -0,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 3,36</t>
+          <t>-10,08; 2,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 5,71</t>
+          <t>-9,09; 6,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 0,44</t>
+          <t>-12,48; 0,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 1,63</t>
+          <t>-8,57; 1,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 3,9</t>
+          <t>-6,41; 4,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -1,8</t>
+          <t>-11,46; -2,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 40,41</t>
+          <t>-54,05; 27,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 52,28</t>
+          <t>-47,38; 55,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 0,03</t>
+          <t>-74,8; -6,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,22; 26,0</t>
+          <t>-50,24; 25,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 46,43</t>
+          <t>-45,31; 51,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 4,68</t>
+          <t>-61,83; 7,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 12,35</t>
+          <t>-45,18; 10,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 30,23</t>
+          <t>-34,73; 31,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,91; -12,72</t>
+          <t>-61,37; -15,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-10,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-12,28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-2,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-10,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,95</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-12,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 6,88</t>
+          <t>-24,91; -2,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 9,0</t>
+          <t>-16,6; 9,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 0,0</t>
+          <t>-24,79; -4,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,61; -1,83</t>
+          <t>-6,65; 7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 10,13</t>
+          <t>-5,32; 8,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,44; -4,46</t>
+          <t>-13,05; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 0,37</t>
+          <t>-12,96; 0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 6,26</t>
+          <t>-9,27; 6,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -2,66</t>
+          <t>-14,63; -2,5</t>
         </is>
       </c>
     </row>
@@ -730,27 +730,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-86,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-32,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>39,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>77,45%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-86,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-32,14%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,24 +788,24 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 283,49</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 275,7</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,41</t>
+          <t>-100,0; 58,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 203,22</t>
+          <t>-82,13; 226,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,83</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,37</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-6,67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-9,88</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,83</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>-6,72</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>-3,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 4,51</t>
+          <t>-12,25; 6,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 1,41</t>
+          <t>-9,5; 13,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 3,46</t>
+          <t>-10,92; 9,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 5,44</t>
+          <t>-18,89; 4,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 13,15</t>
+          <t>-20,83; 1,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 14,75</t>
+          <t>-18,75; 4,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 2,23</t>
+          <t>-11,67; 2,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 4,6</t>
+          <t>-11,68; 4,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 5,34</t>
+          <t>-10,8; 5,08</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-25,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-42,81%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-63,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-50,66%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-25,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>-43,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-21,97%</t>
+          <t>-23,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,0; 67,33</t>
+          <t>-73,53; 120,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,73; 53,83</t>
+          <t>-62,99; 249,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,42; 56,91</t>
+          <t>-70,19; 166,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,96; 104,44</t>
+          <t>-83,18; 75,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 236,0</t>
+          <t>-94,59; 64,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 267,68</t>
+          <t>-83,99; 79,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 28,75</t>
+          <t>-67,36; 30,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,89; 67,61</t>
+          <t>-67,58; 53,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 56,59</t>
+          <t>-63,01; 64,42</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-10,71</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-6,54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,89</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-10,06</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,81</t>
+          <t>-9,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,61</t>
+          <t>-10,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 12,06</t>
+          <t>-11,96; 26,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 18,15</t>
+          <t>-21,25; 13,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 7,96</t>
+          <t>-29,47; 3,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 25,93</t>
+          <t>-26,78; 9,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 15,96</t>
+          <t>-19,95; 17,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 2,8</t>
+          <t>-28,23; 7,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 13,01</t>
+          <t>-13,63; 13,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 10,63</t>
+          <t>-15,58; 10,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 0,62</t>
+          <t>-21,4; 2,66</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-12,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-49,47%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-26,08%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-3,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-40,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-12,32%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-49,96%</t>
+          <t>-38,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-45,53%</t>
+          <t>-44,34%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 99,27</t>
+          <t>-41,13; 228,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 143,14</t>
+          <t>-64,89; 151,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,29; 67,74</t>
+          <t>-85,88; 45,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 208,7</t>
+          <t>-75,16; 74,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,16; 138,38</t>
+          <t>-57,06; 139,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,62; 45,94</t>
+          <t>-79,21; 65,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 75,32</t>
+          <t>-44,3; 81,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 69,33</t>
+          <t>-47,5; 68,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 8,09</t>
+          <t>-70,63; 24,24</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-10,47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,51</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-13,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,35</t>
+          <t>-8,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-12,55</t>
+          <t>-9,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 20,69</t>
+          <t>-14,25; 21,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 22,41</t>
+          <t>-19,16; 16,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-29,33; -0,63</t>
+          <t>-23,35; 3,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 20,85</t>
+          <t>-16,46; 18,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 14,46</t>
+          <t>-14,75; 23,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 0,56</t>
+          <t>-25,56; 3,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 14,55</t>
+          <t>-11,29; 15,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 15,17</t>
+          <t>-12,09; 13,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -3,69</t>
+          <t>-20,77; -0,86</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-11,41%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-45,9%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>10,88%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>17,05%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-63,65%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-11,41%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-49,74%</t>
+          <t>-41,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,47%</t>
+          <t>-43,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 191,77</t>
+          <t>-53,03; 144,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 186,3</t>
+          <t>-67,6; 109,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,88; 1,77</t>
+          <t>-77,45; 28,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,95; 139,56</t>
+          <t>-61,89; 144,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,37; 93,88</t>
+          <t>-60,72; 211,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,17; 10,78</t>
+          <t>-79,54; 45,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 92,23</t>
+          <t>-41,01; 96,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 91,5</t>
+          <t>-49,45; 84,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,68; -22,68</t>
+          <t>-72,45; -4,06</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,58</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-3,39</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,63</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-7,02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-4,62</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,55</t>
+          <t>-5,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,88</t>
+          <t>-9,92; 3,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 6,24</t>
+          <t>-8,46; 5,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -0,56</t>
+          <t>-12,79; 0,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 2,99</t>
+          <t>-10,6; 3,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 6,11</t>
+          <t>-9,21; 6,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 0,74</t>
+          <t>-11,67; 2,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,38</t>
+          <t>-8,18; 1,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 4,03</t>
+          <t>-6,51; 4,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -2,28</t>
+          <t>-10,28; -0,3</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-21,99%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-8,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-36,33%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-21,95%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-10,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-45,44%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-21,99%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-8,87%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-37,21%</t>
+          <t>-29,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,25%</t>
+          <t>-33,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 27,86</t>
+          <t>-50,5; 29,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 55,38</t>
+          <t>-41,9; 46,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,8; -6,13</t>
+          <t>-63,63; 6,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 25,11</t>
+          <t>-52,17; 27,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 51,59</t>
+          <t>-48,12; 50,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 7,15</t>
+          <t>-62,25; 21,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 10,24</t>
+          <t>-44,94; 14,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 31,52</t>
+          <t>-35,98; 35,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,37; -15,04</t>
+          <t>-55,93; -2,26</t>
         </is>
       </c>
     </row>
